--- a/raw/waterbird_trends.xlsx
+++ b/raw/waterbird_trends.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5204897_ad_unsw_edu_au1/Documents/Desktop/Honours_UNSW/Assessment/cumbung_assessment/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{3EE0DBDB-2C40-4C5D-B9C4-9ED8B1FCBB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81CCE27D-F576-4AE7-A748-DAE1A7447443}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{3EE0DBDB-2C40-4C5D-B9C4-9ED8B1FCBB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AD57692-069C-4630-B775-7B56B1380586}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="8" xr2:uid="{65864C75-82C0-4CAE-A255-1A424103F31A}"/>
+    <workbookView xWindow="456" yWindow="276" windowWidth="21492" windowHeight="13164" xr2:uid="{65864C75-82C0-4CAE-A255-1A424103F31A}"/>
   </bookViews>
   <sheets>
     <sheet name="cumbung" sheetId="2" r:id="rId1"/>
@@ -58,7 +58,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#,##0.00\ _X_D_R"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ _X_D_R"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -545,7 +545,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
